--- a/venture_capital_structured.xlsx
+++ b/venture_capital_structured.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://venturecapitalcareers.com/</t>
+          <t>https://www.peakxv.com/</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -514,7 +514,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://jobs.accel.com/</t>
+          <t>https://accelpartners.jobsoid.com/</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -584,7 +584,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://venturecapitalcareers.com/job/1474687-marketing-manager</t>
+          <t>https://z47.com/</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://venturecapitalcareers.com/companies/blume-ventures</t>
+          <t>https://blume.vc/work-with-us</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -654,7 +654,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://venturecapitalcareers.com/job/988052-analyst-kalaari-fellowship</t>
+          <t>https://kalaari.com/jobs/</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://venturecapitalcareers.com/</t>
+          <t>https://nexusvp.com/</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.chiratae.com/careers/</t>
+          <t>https://chiratae.zohorecruit.com/</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1912,11 +1912,7 @@
           <t>Consumer, FinTech, SaaS, Enterprise, AI, DeepTech</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>https://venturecapitalcareers.com/</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/company/tiger-global-management/jobs/</t>
@@ -2054,7 +2050,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://www.temasek.com.sg/en/about-us/careers</t>
+          <t>https://jobs.temasek.com.sg/</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2299,7 +2295,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://jobspaddy.com/careers/job-tag/plumber-jobs/</t>
+          <t>https://job-boards.greenhouse.io/generalatlantic</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2334,7 +2330,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://warburgpincus.com/careers/</t>
+          <t>https://job-boards.greenhouse.io/warburgpincusllc</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2439,7 +2435,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://jobs.accel.com/jobs</t>
+          <t>https://accelpartners.jobsoid.com/</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2474,7 +2470,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://careers.insight.com/careers</t>
+          <t>https://careers.smartrecruiters.com/insightpartners</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
